--- a/out/Attention-Mamba1_repeat_1_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_1_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_1_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.006155536510050297</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.006549199111759663</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.005916438065469265</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.005690197460353374</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.004840756766498089</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.005121744237840176</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.005411011166870594</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.004284597001969814</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.004202387295663357</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.004433517344295979</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.004557807929813862</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.004359773360192776</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.004370830021798611</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.004593384452164173</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.004804410971701145</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.006332497112452984</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.005874377675354481</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.009832230396568775</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.005364890210330486</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.009084378369152546</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.006359660066664219</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0045426981523633</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.004405396990478039</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.005239934660494328</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.004011319018900394</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.004287113435566425</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.00487480778247118</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.003821221180260181</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.004228278063237667</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.004663283936679363</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01153040397912264</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.00458619836717844</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.005045800469815731</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.004638084210455418</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.004021075554192066</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.005088110454380512</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.004553514532744884</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.00428480003029108</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.004547837190330029</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.004658506251871586</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.004647110588848591</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.004016808234155178</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.003898289985954762</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.004344594664871693</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.00410416629165411</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.004113274626433849</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.004385112784802914</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.004028859548270702</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.004402575083076954</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.004289726726710796</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.004703490994870663</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.004296979866921902</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.00415633711963892</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.004716317169368267</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.00422563124448061</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.00587210338562727</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.004394496791064739</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.004776298068463802</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.004574178718030453</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.004131441004574299</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.00466559361666441</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.003945735283195972</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.004055059514939785</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.003910957835614681</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.003720561973750591</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.004207278601825237</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.003876823000609875</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.003878832794725895</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.004302498884499073</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.004163085483014584</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.003948408178985119</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.0051503861322999</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01490217540413141</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.009070155210793018</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.01831258274614811</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01076987478882074</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.009943020530045033</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.00789989810436964</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.00810705404728651</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.008264028467237949</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.008865880779922009</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01111043710261583</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.007837266661226749</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.00938702467828989</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.008013247512280941</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.007105038501322269</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.01313872169703245</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.008965088985860348</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.007594279013574123</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.007379208691418171</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.008176698349416256</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.007667073048651218</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.007642061449587345</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.008460125885903835</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.009511169977486134</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.007779247127473354</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.007847587577998638</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.00811465922743082</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.007255309261381626</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.00827417615801096</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01016536075621843</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.008152549155056477</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.008170568384230137</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.009293354116380215</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.009642587043344975</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.007930519990622997</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.009661092422902584</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.008663400076329708</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.009030387736856937</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.008067586459219456</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.008250216953456402</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.008878684602677822</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.03032833710312843</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.01101031620055437</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.03709295392036438</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.0168562289327383</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.0230396930128336</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01169995125383139</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.009509108029305935</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.00894737895578146</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.02566426992416382</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.01851473748683929</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.0397208034992218</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.007427711971104145</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.6500000000000004</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.007494001649320126</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_1_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000005.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.006155536510050297</v>
+        <v>0.006155543960630894</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.006549199111759663</v>
+        <v>0.006549178622663021</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.005916438065469265</v>
+        <v>0.005916432477533817</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.005690197460353374</v>
+        <v>0.005690176971256733</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.004840756766498089</v>
+        <v>0.004840771667659283</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.005121744237840176</v>
+        <v>0.005121761001646519</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.005411011166870594</v>
+        <v>0.005411040969192982</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.004284597001969814</v>
+        <v>0.004284604452550411</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.004202387295663357</v>
+        <v>0.004202381707727909</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.004433517344295979</v>
+        <v>0.004433500580489635</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.004557807929813862</v>
+        <v>0.004557794891297817</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.004359773360192776</v>
+        <v>0.00435981247574091</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.004370830021798611</v>
+        <v>0.004370852373540401</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.2599999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.004593384452164173</v>
+        <v>0.00459339190274477</v>
       </c>
       <c r="JB15" t="n">
         <v>0.02000000000000007</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.004804410971701145</v>
+        <v>0.004804405383765697</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.006332497112452984</v>
+        <v>0.006332485936582088</v>
       </c>
       <c r="JB17" t="n">
         <v>0.5799999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.005874377675354481</v>
+        <v>0.005874381400644779</v>
       </c>
       <c r="JB18" t="n">
         <v>0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.009832230396568775</v>
+        <v>0.009832222945988178</v>
       </c>
       <c r="JB19" t="n">
         <v>0.8599999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.005364890210330486</v>
+        <v>0.005364843644201756</v>
       </c>
       <c r="JB20" t="n">
         <v>0.8599999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.009084378369152546</v>
+        <v>0.0090843690559268</v>
       </c>
       <c r="JB21" t="n">
         <v>0.5799999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.006359660066664219</v>
+        <v>0.006359689868986607</v>
       </c>
       <c r="JB22" t="n">
         <v>0.3</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.0045426981523633</v>
+        <v>0.004542707465589046</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.3</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.004405396990478039</v>
+        <v>0.004405411891639233</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.005239934660494328</v>
+        <v>0.005239925347268581</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.8599999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.004011319018900394</v>
+        <v>0.004011324606835842</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.8599999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.004287113435566425</v>
+        <v>0.004287098534405231</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.00487480778247118</v>
+        <v>0.004874811507761478</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.003821221180260181</v>
+        <v>0.003821223042905331</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.004228278063237667</v>
+        <v>0.004228251986205578</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.004663283936679363</v>
+        <v>0.004663272760808468</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.7199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.01153040397912264</v>
+        <v>0.01153041515499353</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.1199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.00458619836717844</v>
+        <v>0.004586166702210903</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.1199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.005045800469815731</v>
+        <v>0.005045791156589985</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.1199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.004638084210455418</v>
+        <v>0.004638087935745716</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.2599999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.004021075554192066</v>
+        <v>0.004021077416837215</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.2599999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.005088110454380512</v>
+        <v>0.00508811604231596</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.004553514532744884</v>
+        <v>0.004553527571260929</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.8599999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.00428480003029108</v>
+        <v>0.004284805618226528</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.004547837190330029</v>
+        <v>0.004547826014459133</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.004658506251871586</v>
+        <v>0.004658491350710392</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.004647110588848591</v>
+        <v>0.00464711245149374</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.004016808234155178</v>
+        <v>0.004016798920929432</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.003898289985954762</v>
+        <v>0.003898278810083866</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.004344594664871693</v>
+        <v>0.00434460025280714</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.00410416629165411</v>
+        <v>0.004104173742234707</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.004113274626433849</v>
+        <v>0.004113278351724148</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.004385112784802914</v>
+        <v>0.00438507366925478</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.004028859548270702</v>
+        <v>0.004028861410915852</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.004402575083076954</v>
+        <v>0.004402588121592999</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.2599999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.004289726726710796</v>
+        <v>0.004289732314646244</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.2599999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.004703490994870663</v>
+        <v>0.004703485406935215</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.2599999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.004296979866921902</v>
+        <v>0.004296989180147648</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.1199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.004716317169368267</v>
+        <v>0.00471633393317461</v>
       </c>
       <c r="JB55" t="n">
         <v>0.02000000000000007</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.00422563124448061</v>
+        <v>0.004225677810609341</v>
       </c>
       <c r="JB56" t="n">
         <v>0.16</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.00587210338562727</v>
+        <v>0.005872082896530628</v>
       </c>
       <c r="JB57" t="n">
         <v>0.3</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.004394496791064739</v>
+        <v>0.004394509829580784</v>
       </c>
       <c r="JB58" t="n">
         <v>0.3</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.004574178718030453</v>
+        <v>0.004574143327772617</v>
       </c>
       <c r="JB60" t="n">
         <v>0.16</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.004131441004574299</v>
+        <v>0.004131457768380642</v>
       </c>
       <c r="JB61" t="n">
         <v>0.02000000000000007</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.00466559361666441</v>
+        <v>0.004665589891374111</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.004055059514939785</v>
+        <v>0.004055089317262173</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.8599999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.003910957835614681</v>
+        <v>0.003910972736775875</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.8599999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.003720561973750591</v>
+        <v>0.003720560111105442</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.8599999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.004207278601825237</v>
+        <v>0.004207304678857327</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.8599999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.003876823000609875</v>
+        <v>0.003876839764416218</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.003878832794725895</v>
+        <v>0.003878821618855</v>
       </c>
       <c r="JB69" t="n">
         <v>0.02000000000000007</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.004302498884499073</v>
+        <v>0.004302493296563625</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.1199999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.004163085483014584</v>
+        <v>0.004163102246820927</v>
       </c>
       <c r="JB71" t="n">
         <v>0.16</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.003948408178985119</v>
+        <v>0.00394843053072691</v>
       </c>
       <c r="JB72" t="n">
         <v>0.4399999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.0051503861322999</v>
+        <v>0.005150376819074154</v>
       </c>
       <c r="JB73" t="n">
         <v>0.5799999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.01490217540413141</v>
+        <v>0.01490213442593813</v>
       </c>
       <c r="JB74" t="n">
         <v>0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.009070155210793018</v>
+        <v>0.009070149622857571</v>
       </c>
       <c r="JB75" t="n">
         <v>0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.01831258274614811</v>
+        <v>0.01831255480647087</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.01076987478882074</v>
+        <v>0.01076985243707895</v>
       </c>
       <c r="JB77" t="n">
         <v>0.8599999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.009943020530045033</v>
+        <v>0.009943014942109585</v>
       </c>
       <c r="JB78" t="n">
         <v>0.7199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.00789989810436964</v>
+        <v>0.007899896241724491</v>
       </c>
       <c r="JB79" t="n">
         <v>0.5799999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.008264028467237949</v>
+        <v>0.008264024741947651</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.16</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.008865880779922009</v>
+        <v>0.008865884505212307</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.16</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.01111043710261583</v>
+        <v>0.01111042592674494</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.007837266661226749</v>
+        <v>0.007837249897420406</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.02000000000000007</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.00938702467828989</v>
+        <v>0.009387009777128696</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.008013247512280941</v>
+        <v>0.008013227023184299</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.02000000000000007</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.007105038501322269</v>
+        <v>0.007105021737515926</v>
       </c>
       <c r="JB87" t="n">
         <v>0.7199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.01313872169703245</v>
+        <v>0.01313874032348394</v>
       </c>
       <c r="JB88" t="n">
         <v>0.5799999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.008965088985860348</v>
+        <v>0.008965075947344303</v>
       </c>
       <c r="JB89" t="n">
         <v>0.5799999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.007594279013574123</v>
+        <v>0.007594318129122257</v>
       </c>
       <c r="JB90" t="n">
         <v>0.7199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.007379208691418171</v>
+        <v>0.00737921055406332</v>
       </c>
       <c r="JB91" t="n">
         <v>0.5799999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.008176698349416256</v>
+        <v>0.008176709525287151</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.16</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.007667073048651218</v>
+        <v>0.007667086087167263</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.02000000000000007</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.007642061449587345</v>
+        <v>0.007642070762813091</v>
       </c>
       <c r="JB94" t="n">
         <v>0.1199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.009511169977486134</v>
+        <v>0.009511164389550686</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.3</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.007779247127473354</v>
+        <v>0.007779230363667011</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.007847587577998638</v>
+        <v>0.007847539149224758</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.00811465922743082</v>
+        <v>0.008114677853882313</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.007255309261381626</v>
+        <v>0.007255311124026775</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.00827417615801096</v>
+        <v>0.008274185471236706</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.01016536075621843</v>
+        <v>0.01016531605273485</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.008152549155056477</v>
+        <v>0.008152530528604984</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.4399999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.008170568384230137</v>
+        <v>0.008170553483068943</v>
       </c>
       <c r="JB104" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.009293354116380215</v>
+        <v>0.009293355979025364</v>
       </c>
       <c r="JB105" t="n">
         <v>0.1600000000000001</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.009642587043344975</v>
+        <v>0.009642585180699825</v>
       </c>
       <c r="JB106" t="n">
         <v>0.4399999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.007930519990622997</v>
+        <v>0.00793051440268755</v>
       </c>
       <c r="JB107" t="n">
         <v>0.5799999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.009661092422902584</v>
+        <v>0.009661099873483181</v>
       </c>
       <c r="JB108" t="n">
         <v>0.4399999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.008663400076329708</v>
+        <v>0.00866342056542635</v>
       </c>
       <c r="JB109" t="n">
         <v>0.16</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.009030387736856937</v>
+        <v>0.009030376560986042</v>
       </c>
       <c r="JB110" t="n">
         <v>0.16</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.008067586459219456</v>
+        <v>0.00806757714599371</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.5799999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.008250216953456402</v>
+        <v>0.008250207640230656</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.4399999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.008878684602677822</v>
+        <v>0.008878716267645359</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.01101031620055437</v>
+        <v>0.01101030688732862</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.03709295392036438</v>
+        <v>0.03709294646978378</v>
       </c>
       <c r="JB116" t="n">
         <v>0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.0168562289327383</v>
+        <v>0.01685621030628681</v>
       </c>
       <c r="JB117" t="n">
         <v>0.8599999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.0230396930128336</v>
+        <v>0.02303972095251083</v>
       </c>
       <c r="JB118" t="n">
         <v>0.5799999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.01169995125383139</v>
+        <v>0.01169994752854109</v>
       </c>
       <c r="JB119" t="n">
         <v>0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.009509108029305935</v>
+        <v>0.00950914341956377</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.3</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.00894737895578146</v>
+        <v>0.008947408758103848</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.02566426992416382</v>
+        <v>0.02566429600119591</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.01851473748683929</v>
+        <v>0.01851472072303295</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.0397208034992218</v>
+        <v>0.0397208072245121</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.007427711971104145</v>
+        <v>0.007427713833749294</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.6500000000000004</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.007494001649320126</v>
+        <v>0.007493973709642887</v>
       </c>
       <c r="JB126" t="n">
         <v>-1</v>
